--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149419</v>
+        <v>121149417</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530682</v>
+        <v>530681</v>
       </c>
       <c r="R2" t="n">
-        <v>6832998</v>
+        <v>6832966</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149418</v>
+        <v>121149420</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530673</v>
+        <v>530700</v>
       </c>
       <c r="R3" t="n">
-        <v>6832997</v>
+        <v>6832992</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149420</v>
+        <v>121149418</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530700</v>
+        <v>530673</v>
       </c>
       <c r="R4" t="n">
-        <v>6832992</v>
+        <v>6832997</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121149416</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149417</v>
+        <v>121149419</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530681</v>
+        <v>530682</v>
       </c>
       <c r="R6" t="n">
-        <v>6832966</v>
+        <v>6832998</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149417</v>
+        <v>121149416</v>
       </c>
       <c r="B2" t="n">
         <v>98081</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530681</v>
+        <v>530706</v>
       </c>
       <c r="R2" t="n">
-        <v>6832966</v>
+        <v>6832934</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149420</v>
+        <v>121149419</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530700</v>
+        <v>530682</v>
       </c>
       <c r="R3" t="n">
-        <v>6832992</v>
+        <v>6832998</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149418</v>
+        <v>121149420</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530673</v>
+        <v>530700</v>
       </c>
       <c r="R4" t="n">
-        <v>6832997</v>
+        <v>6832992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149416</v>
+        <v>121149417</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530706</v>
+        <v>530681</v>
       </c>
       <c r="R5" t="n">
-        <v>6832934</v>
+        <v>6832966</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149419</v>
+        <v>121149418</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530682</v>
+        <v>530673</v>
       </c>
       <c r="R6" t="n">
-        <v>6832998</v>
+        <v>6832997</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121149416</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149419</v>
+        <v>121149417</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530682</v>
+        <v>530681</v>
       </c>
       <c r="R3" t="n">
-        <v>6832998</v>
+        <v>6832966</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149420</v>
+        <v>121149419</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530700</v>
+        <v>530682</v>
       </c>
       <c r="R4" t="n">
-        <v>6832992</v>
+        <v>6832998</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149417</v>
+        <v>121149418</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530681</v>
+        <v>530673</v>
       </c>
       <c r="R5" t="n">
-        <v>6832966</v>
+        <v>6832997</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149418</v>
+        <v>121149420</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530673</v>
+        <v>530700</v>
       </c>
       <c r="R6" t="n">
-        <v>6832997</v>
+        <v>6832992</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149416</v>
+        <v>121149419</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530706</v>
+        <v>530682</v>
       </c>
       <c r="R2" t="n">
-        <v>6832934</v>
+        <v>6832998</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149417</v>
+        <v>121149416</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530681</v>
+        <v>530706</v>
       </c>
       <c r="R3" t="n">
-        <v>6832966</v>
+        <v>6832934</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149419</v>
+        <v>121149418</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530682</v>
+        <v>530673</v>
       </c>
       <c r="R4" t="n">
-        <v>6832998</v>
+        <v>6832997</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149418</v>
+        <v>121149417</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530673</v>
+        <v>530681</v>
       </c>
       <c r="R5" t="n">
-        <v>6832997</v>
+        <v>6832966</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149419</v>
+        <v>121149418</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530682</v>
+        <v>530673</v>
       </c>
       <c r="R2" t="n">
-        <v>6832998</v>
+        <v>6832997</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149416</v>
+        <v>121149419</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530706</v>
+        <v>530682</v>
       </c>
       <c r="R3" t="n">
-        <v>6832934</v>
+        <v>6832998</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149418</v>
+        <v>121149420</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530673</v>
+        <v>530700</v>
       </c>
       <c r="R4" t="n">
-        <v>6832997</v>
+        <v>6832992</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>121149417</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149420</v>
+        <v>121149416</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530700</v>
+        <v>530706</v>
       </c>
       <c r="R6" t="n">
-        <v>6832992</v>
+        <v>6832934</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149418</v>
+        <v>121149419</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530673</v>
+        <v>530682</v>
       </c>
       <c r="R2" t="n">
-        <v>6832997</v>
+        <v>6832998</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149419</v>
+        <v>121149417</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530682</v>
+        <v>530681</v>
       </c>
       <c r="R3" t="n">
-        <v>6832998</v>
+        <v>6832966</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149417</v>
+        <v>121149416</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530681</v>
+        <v>530706</v>
       </c>
       <c r="R5" t="n">
-        <v>6832966</v>
+        <v>6832934</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149416</v>
+        <v>121149418</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530706</v>
+        <v>530673</v>
       </c>
       <c r="R6" t="n">
-        <v>6832934</v>
+        <v>6832997</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 37642-2021 artfynd.xlsx
+++ b/artfynd/A 37642-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149419</v>
+        <v>121149420</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530682</v>
+        <v>530700</v>
       </c>
       <c r="R2" t="n">
-        <v>6832998</v>
+        <v>6832992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121149417</v>
+        <v>121149416</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530681</v>
+        <v>530706</v>
       </c>
       <c r="R3" t="n">
-        <v>6832966</v>
+        <v>6832934</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149420</v>
+        <v>121149417</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530700</v>
+        <v>530681</v>
       </c>
       <c r="R4" t="n">
-        <v>6832992</v>
+        <v>6832966</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121149416</v>
+        <v>121149418</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530706</v>
+        <v>530673</v>
       </c>
       <c r="R5" t="n">
-        <v>6832934</v>
+        <v>6832997</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149418</v>
+        <v>121149419</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530673</v>
+        <v>530682</v>
       </c>
       <c r="R6" t="n">
-        <v>6832997</v>
+        <v>6832998</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
